--- a/create_forecast_basic/future/iplan/Intermediates/240703_pop_2040_iplan.xlsx
+++ b/create_forecast_basic/future/iplan/Intermediates/240703_pop_2040_iplan.xlsx
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1371.273315235244</v>
+        <v>1371.273315235243</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>4230.221759271561</v>
+        <v>4230.221759271563</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3740.185381028129</v>
+        <v>3740.185381028132</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>17240.23018612379</v>
+        <v>17240.23018612378</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>9777.73266842325</v>
+        <v>9777.732668423241</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>16807.00538496573</v>
+        <v>16807.00538496575</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>44090.74070513907</v>
+        <v>44090.74070513909</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>32594.48113606609</v>
+        <v>32594.48113606606</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1648.825023696268</v>
+        <v>1648.825023696269</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>8078.307912329714</v>
+        <v>8078.307912329716</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2810.105803557798</v>
+        <v>2810.105803557799</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2548.671246382425</v>
+        <v>2548.671246382426</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>14562.88424001715</v>
+        <v>14562.88424001713</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3434.418882239568</v>
+        <v>3434.418882239565</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>8528.634095669826</v>
+        <v>8528.63409566981</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>7867.753658001444</v>
+        <v>7867.753658001441</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>41205.49866103204</v>
+        <v>41205.49866103206</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>11010.74630454678</v>
+        <v>11010.74630454679</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>13914.25831762753</v>
+        <v>13914.25831762752</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>29883.98482964802</v>
+        <v>29883.98482964803</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>6816.390350938424</v>
+        <v>6816.390350938429</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>5744.921008708925</v>
+        <v>5744.921008708924</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>4508.146104760076</v>
+        <v>4508.146104760075</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>712.0389003554238</v>
+        <v>712.0389003554236</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>4065.34177725817</v>
+        <v>4065.341777258173</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>2675.119308975952</v>
+        <v>2675.119308975951</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4540.013119907145</v>
+        <v>4540.013119907146</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7688.976093768694</v>
+        <v>7688.976093768692</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>3808.780392796072</v>
+        <v>3808.780392796074</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>4721.016544771003</v>
+        <v>4721.016544771004</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5279.512793185975</v>
+        <v>5279.512793185974</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>6058.436836672232</v>
+        <v>6058.436836672234</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>8976.027627723119</v>
+        <v>8976.027627723115</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>6285.813162421522</v>
+        <v>6285.81316242152</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>7862.015442828685</v>
+        <v>7862.015442828684</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>57478.63854531751</v>
+        <v>57478.63854531754</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>49822.08963675776</v>
+        <v>49822.08963675774</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>53692.00226821002</v>
+        <v>53692.00226820999</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>57410.05586562878</v>
+        <v>57410.05586562879</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>69796.92097183417</v>
+        <v>69796.92097183419</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>87242.05431125202</v>
+        <v>87242.05431125195</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1876.468180594003</v>
+        <v>1876.468180594002</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>15965.42215612852</v>
+        <v>15965.4221561285</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>9442.747057392524</v>
+        <v>9442.747057392526</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>9208.339121645828</v>
+        <v>9208.339121645831</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>3461.508374855664</v>
+        <v>3461.508374855663</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>4579.689413153123</v>
+        <v>4579.689413153125</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>15058.50597903036</v>
+        <v>15058.50597903035</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>5430.952579312494</v>
+        <v>5430.952579312495</v>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>29465.5095659371</v>
+        <v>29465.50956593708</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>18151.06774510583</v>
+        <v>18151.06774510585</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>73044.12736216636</v>
+        <v>73044.12736216643</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>13012.77442273422</v>
+        <v>13012.77442273421</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>24300.74054397946</v>
+        <v>24300.74054397947</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>30731.30061755627</v>
+        <v>30731.30061755625</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>43006.22692765288</v>
+        <v>43006.2269276529</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>8879.322577358715</v>
+        <v>8879.322577358716</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>10668.08003875793</v>
+        <v>10668.08003875794</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>7087.788089231012</v>
+        <v>7087.78808923101</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>3782.610119927699</v>
+        <v>3782.610119927701</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>5089.807075229009</v>
+        <v>5089.807075229008</v>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>12764.19512247559</v>
+        <v>12764.1951224756</v>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>9713.585768914581</v>
+        <v>9713.585768914578</v>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>88290.55663788278</v>
+        <v>88290.55663788275</v>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>13500.57804742779</v>
+        <v>13500.57804742778</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>7730.312762644214</v>
+        <v>7730.312762644211</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>48124.39250075501</v>
+        <v>48124.392500755</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>32995.4521136471</v>
+        <v>32995.45211364709</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>45633.90824918672</v>
+        <v>45633.90824918677</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>34182.00799840569</v>
+        <v>34182.00799840568</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
